--- a/northstar_mc/outputs/summary.xlsx
+++ b/northstar_mc/outputs/summary.xlsx
@@ -3689,7 +3689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4044,6 +4044,30 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>baseline_financials</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>baseline_passthrough</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
